--- a/resources/Student_Template.xlsx
+++ b/resources/Student_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Iness_Tasks\Task1\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB65F43E-81BE-44CF-8E7F-BFD353B1E2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E547123-6104-4E7E-ADBC-D088DEA10E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -406,11 +406,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="4" max="4" width="31.33203125" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="27.88671875" customWidth="1"/>
+    <col min="6" max="6" width="42.44140625" customWidth="1"/>
     <col min="7" max="7" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
